--- a/utils/monday_sprint_sprint_2025-18.xlsx
+++ b/utils/monday_sprint_sprint_2025-18.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="261">
   <si>
     <t>Ticket</t>
   </si>
@@ -117,6 +117,9 @@
     <t>06/06/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
@@ -168,7 +171,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -324,7 +327,7 @@
     <t>25/06/2025</t>
   </si>
   <si>
-    <t>22/03/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>33420</t>
@@ -1389,21 +1392,21 @@
         <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -1415,10 +1418,10 @@
         <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>25</v>
@@ -1436,10 +1439,10 @@
         <v>17</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>17</v>
@@ -1447,22 +1450,22 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>19</v>
@@ -1491,22 +1494,22 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>19</v>
@@ -1524,7 +1527,7 @@
         <v>17</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>21</v>
@@ -1535,37 +1538,37 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>20</v>
@@ -1574,27 +1577,27 @@
         <v>21</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>19</v>
@@ -1623,22 +1626,22 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>19</v>
@@ -1656,10 +1659,10 @@
         <v>17</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>17</v>
@@ -1667,66 +1670,66 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>19</v>
@@ -1747,7 +1750,7 @@
         <v>20</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>17</v>
@@ -1755,22 +1758,22 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>19</v>
@@ -1788,10 +1791,10 @@
         <v>17</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>17</v>
@@ -1799,22 +1802,22 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>19</v>
@@ -1843,22 +1846,22 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>19</v>
@@ -1887,22 +1890,22 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>19</v>
@@ -1920,10 +1923,10 @@
         <v>17</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>17</v>
@@ -1931,22 +1934,22 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>25</v>
@@ -1964,7 +1967,7 @@
         <v>17</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>21</v>
@@ -1975,22 +1978,22 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>19</v>
@@ -2008,10 +2011,10 @@
         <v>17</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>17</v>
@@ -2019,22 +2022,22 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>19</v>
@@ -2052,7 +2055,7 @@
         <v>17</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>21</v>
@@ -2063,22 +2066,22 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
@@ -2096,7 +2099,7 @@
         <v>17</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>21</v>
@@ -2107,19 +2110,19 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>17</v>
@@ -2128,13 +2131,13 @@
         <v>25</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>17</v>
@@ -2146,24 +2149,24 @@
         <v>21</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>17</v>
@@ -2172,42 +2175,42 @@
         <v>25</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>17</v>
@@ -2216,45 +2219,45 @@
         <v>25</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
@@ -2272,7 +2275,7 @@
         <v>17</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>21</v>
@@ -2283,22 +2286,22 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
@@ -2316,7 +2319,7 @@
         <v>17</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>21</v>
@@ -2327,22 +2330,22 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2360,10 +2363,10 @@
         <v>17</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>17</v>
@@ -2371,22 +2374,22 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>19</v>
@@ -2404,7 +2407,7 @@
         <v>17</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>21</v>
@@ -2415,66 +2418,66 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2492,7 +2495,7 @@
         <v>17</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>21</v>
@@ -2503,22 +2506,22 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>19</v>
@@ -2547,22 +2550,22 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2580,7 +2583,7 @@
         <v>17</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>21</v>
@@ -2591,22 +2594,22 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>19</v>
@@ -2635,22 +2638,22 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>19</v>
@@ -2671,7 +2674,7 @@
         <v>20</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>17</v>
@@ -2679,22 +2682,22 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
@@ -2712,7 +2715,7 @@
         <v>17</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>21</v>
@@ -2723,22 +2726,22 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
@@ -2767,22 +2770,22 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2800,10 +2803,10 @@
         <v>17</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>17</v>
@@ -2811,22 +2814,22 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>19</v>
@@ -2855,66 +2858,66 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>19</v>
@@ -2932,7 +2935,7 @@
         <v>17</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>21</v>
@@ -2943,34 +2946,34 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>17</v>
@@ -2982,27 +2985,27 @@
         <v>21</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>19</v>
@@ -3020,7 +3023,7 @@
         <v>17</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>21</v>
@@ -3031,22 +3034,22 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -3064,7 +3067,7 @@
         <v>17</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>21</v>
@@ -3075,22 +3078,22 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>19</v>
@@ -3108,7 +3111,7 @@
         <v>17</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>21</v>
@@ -3119,22 +3122,22 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -3152,7 +3155,7 @@
         <v>17</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>21</v>
@@ -3163,22 +3166,22 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>19</v>
@@ -3196,7 +3199,7 @@
         <v>17</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>21</v>
@@ -3207,22 +3210,22 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3251,22 +3254,22 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3284,7 +3287,7 @@
         <v>17</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>21</v>
@@ -3295,22 +3298,22 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3328,7 +3331,7 @@
         <v>17</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>21</v>
@@ -3339,22 +3342,22 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3372,7 +3375,7 @@
         <v>17</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>21</v>
@@ -3383,22 +3386,22 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
@@ -3416,10 +3419,10 @@
         <v>17</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>17</v>
@@ -3427,22 +3430,22 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3471,22 +3474,22 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
@@ -3504,10 +3507,10 @@
         <v>17</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>17</v>
@@ -3515,22 +3518,22 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
@@ -3548,7 +3551,7 @@
         <v>17</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>21</v>
@@ -3559,22 +3562,22 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>19</v>
@@ -3595,7 +3598,7 @@
         <v>20</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>17</v>
@@ -3603,22 +3606,22 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3636,10 +3639,10 @@
         <v>17</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>17</v>
@@ -3647,22 +3650,22 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3680,7 +3683,7 @@
         <v>17</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M56" s="2" t="s">
         <v>21</v>
@@ -3691,22 +3694,22 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3724,7 +3727,7 @@
         <v>17</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>21</v>
@@ -3735,22 +3738,22 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3768,7 +3771,7 @@
         <v>17</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>21</v>
@@ -3779,22 +3782,22 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -3812,7 +3815,7 @@
         <v>17</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>21</v>
@@ -3823,22 +3826,22 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>25</v>
@@ -3856,7 +3859,7 @@
         <v>17</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>21</v>
@@ -3867,28 +3870,28 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>32</v>
@@ -3903,30 +3906,30 @@
         <v>20</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -3944,7 +3947,7 @@
         <v>17</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>21</v>
@@ -3955,22 +3958,22 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -3988,7 +3991,7 @@
         <v>17</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>21</v>
@@ -3999,22 +4002,22 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4032,7 +4035,7 @@
         <v>17</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>21</v>
@@ -4043,22 +4046,22 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>19</v>
@@ -4076,7 +4079,7 @@
         <v>17</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>21</v>
@@ -4087,22 +4090,22 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -4120,7 +4123,7 @@
         <v>17</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>21</v>
@@ -4131,22 +4134,22 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4164,10 +4167,10 @@
         <v>17</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>17</v>
@@ -4175,22 +4178,22 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4208,7 +4211,7 @@
         <v>17</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>21</v>
@@ -4219,22 +4222,22 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
@@ -4252,7 +4255,7 @@
         <v>17</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>21</v>
@@ -4263,22 +4266,22 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
@@ -4296,7 +4299,7 @@
         <v>17</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>21</v>
@@ -4307,22 +4310,22 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>19</v>
@@ -4340,7 +4343,7 @@
         <v>17</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>21</v>
@@ -4351,22 +4354,22 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4384,7 +4387,7 @@
         <v>17</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>21</v>
@@ -4395,22 +4398,22 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>25</v>
@@ -4428,7 +4431,7 @@
         <v>17</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>21</v>
@@ -4439,22 +4442,22 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4472,7 +4475,7 @@
         <v>17</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>21</v>
@@ -4483,22 +4486,22 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
@@ -4516,7 +4519,7 @@
         <v>17</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M75" s="2" t="s">
         <v>21</v>
@@ -4527,22 +4530,22 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4560,10 +4563,10 @@
         <v>17</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>17</v>
@@ -4571,7 +4574,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4583,10 +4586,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
@@ -4604,7 +4607,7 @@
         <v>17</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>21</v>
@@ -4615,7 +4618,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4627,10 +4630,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4648,7 +4651,7 @@
         <v>17</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>21</v>
@@ -4659,7 +4662,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -4671,10 +4674,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>19</v>
@@ -4692,7 +4695,7 @@
         <v>17</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>21</v>
@@ -4703,7 +4706,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4715,10 +4718,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>19</v>
@@ -4736,7 +4739,7 @@
         <v>17</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>21</v>
@@ -4747,7 +4750,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4759,10 +4762,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>19</v>
@@ -4780,7 +4783,7 @@
         <v>17</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>21</v>
@@ -4791,7 +4794,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -4803,10 +4806,10 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>19</v>
@@ -4824,7 +4827,7 @@
         <v>17</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M82" s="2" t="s">
         <v>21</v>
@@ -4835,7 +4838,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -4847,10 +4850,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4868,7 +4871,7 @@
         <v>17</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M83" s="2" t="s">
         <v>21</v>
@@ -4879,22 +4882,22 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>19</v>
@@ -4915,7 +4918,7 @@
         <v>20</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>17</v>
@@ -4923,22 +4926,22 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
@@ -4959,7 +4962,7 @@
         <v>20</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>17</v>
@@ -4967,22 +4970,22 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
@@ -5000,10 +5003,10 @@
         <v>17</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>17</v>
@@ -5011,22 +5014,22 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>19</v>
@@ -5044,7 +5047,7 @@
         <v>17</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M87" s="2" t="s">
         <v>21</v>
@@ -5055,22 +5058,22 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>19</v>
@@ -5088,7 +5091,7 @@
         <v>17</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>21</v>
@@ -5099,22 +5102,22 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>19</v>
@@ -5132,7 +5135,7 @@
         <v>17</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M89" s="2" t="s">
         <v>21</v>
@@ -5143,22 +5146,22 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>19</v>
@@ -5176,7 +5179,7 @@
         <v>17</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>21</v>
@@ -5198,23 +5201,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5222,16 +5225,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5250,12 +5253,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K22">
         <v>54</v>
@@ -5263,7 +5266,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -5271,7 +5274,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5302,12 +5305,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B2">
         <v>89</v>
@@ -5331,25 +5334,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5360,31 +5363,31 @@
         <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10">
         <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N10">
         <v>54</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -5404,7 +5407,7 @@
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K11">
         <v>89</v>
@@ -5416,15 +5419,15 @@
         <v>21</v>
       </c>
       <c r="P11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -5436,7 +5439,7 @@
         <v>79</v>
       </c>
       <c r="M12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -5445,30 +5448,30 @@
         <v>21</v>
       </c>
       <c r="Q12">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N13">
         <v>6</v>
       </c>
       <c r="P13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q13">
         <v>1</v>
@@ -5482,13 +5485,13 @@
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -5504,7 +5507,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5512,7 +5515,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5520,7 +5523,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -5531,7 +5534,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5539,44 +5542,44 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5587,7 +5590,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>29</v>
@@ -5595,86 +5598,86 @@
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-18.xlsx
+++ b/utils/monday_sprint_sprint_2025-18.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="281">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>30903</t>
+    <t>9889573518</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,216 +87,231 @@
     <t>25/08/2025</t>
   </si>
   <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>9889573659</t>
+  </si>
+  <si>
+    <t>Novo Recurso</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de aplicação de custos por refugo</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>04/09/2025</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>32133</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Automatização planilha comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
+  </si>
+  <si>
+    <t>Jacson Schneider Movidesk</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>11/08/2025</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>9788042100</t>
+  </si>
+  <si>
+    <t>BI para análises das auditorias de CIPA</t>
+  </si>
+  <si>
+    <t>07/09/2025</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>9880337252</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Atualização de Metas</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>27/08/2025</t>
+  </si>
+  <si>
+    <t>9880303750</t>
+  </si>
+  <si>
+    <t>Melhoria em relatório</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>9889573213</t>
+  </si>
+  <si>
+    <t>Consulta de divergências - Registro Pintura</t>
+  </si>
+  <si>
+    <t>9889573340</t>
+  </si>
+  <si>
+    <t>PDI - Inspeção - Cotas informadas.</t>
+  </si>
+  <si>
+    <t>9787746833</t>
+  </si>
+  <si>
+    <t>ACVO - REUNIÃO</t>
+  </si>
+  <si>
+    <t>06/09/2025</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>9889574229</t>
+  </si>
+  <si>
+    <t>Melhoria Sistema de Custeio - Usinagem Pintura - Revisão de Calculo</t>
+  </si>
+  <si>
+    <t>9067565518</t>
+  </si>
+  <si>
+    <t>Interface Planilhas Custeio Gerencial x Sistema de Custeio - Acompanhamento</t>
+  </si>
+  <si>
+    <t>05/05/2025</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>9704480615</t>
+  </si>
+  <si>
+    <t>Registro K260 – Registro da produção refugada</t>
+  </si>
+  <si>
+    <t>30/07/2025</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>9673898994</t>
+  </si>
+  <si>
+    <t>Sistema de Panelas</t>
+  </si>
+  <si>
+    <t>25/07/2025</t>
+  </si>
+  <si>
+    <t>9889574034</t>
+  </si>
+  <si>
+    <t>PDI - Fixar colunas de identificação das cotas</t>
+  </si>
+  <si>
+    <t>9778063171</t>
+  </si>
+  <si>
+    <t>Sistema de cadastro</t>
+  </si>
+  <si>
+    <t>08/08/2025</t>
+  </si>
+  <si>
+    <t>03/09/2025</t>
+  </si>
+  <si>
+    <t>9674157121</t>
+  </si>
+  <si>
+    <t>Controle de indicadores ao vivo</t>
+  </si>
+  <si>
+    <t>02/09/2025</t>
+  </si>
+  <si>
+    <t>9787746655</t>
+  </si>
+  <si>
+    <t>Retirar de peças do deposito para versão WMS</t>
+  </si>
+  <si>
+    <t>9890031674</t>
+  </si>
+  <si>
+    <t>Teste com Trigger - Checagem do fechamento do custo</t>
+  </si>
+  <si>
+    <t>9879641867</t>
+  </si>
+  <si>
+    <t>Bloco K - Ajuste no filtro de seleção das sequências oriundas do cálculo do custo.</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Integração CRM - Tarefa para disparar integrações</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>33023</t>
-  </si>
-  <si>
-    <t>Novo Recurso</t>
-  </si>
-  <si>
-    <t>Desenvolvimento de aplicação de custos por refugo</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>32133</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Automatização planilha comercial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
-  </si>
-  <si>
-    <t>Jacson Schneider Movidesk</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>11/08/2025</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>32404</t>
-  </si>
-  <si>
-    <t>BI para análises das auditorias de CIPA</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>33412</t>
-  </si>
-  <si>
-    <t>Melhoria</t>
-  </si>
-  <si>
-    <t>Atualização de Metas</t>
-  </si>
-  <si>
-    <t>22/08/2025</t>
-  </si>
-  <si>
-    <t>33421</t>
-  </si>
-  <si>
-    <t>Melhoria em relatório</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>19909</t>
-  </si>
-  <si>
-    <t>Consulta de divergências - Registro Pintura</t>
-  </si>
-  <si>
-    <t>32677</t>
-  </si>
-  <si>
-    <t>PDI - Inspeção - Cotas informadas.</t>
-  </si>
-  <si>
-    <t>30905</t>
-  </si>
-  <si>
-    <t>ACVO - REUNIÃO</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>32353</t>
-  </si>
-  <si>
-    <t>Melhoria Sistema de Custeio - Usinagem Pintura - Revisão de Calculo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexandre, bom dia! Para Custeio Usinagem Pintura, ao invés de utilizar apontamentos de horas, valores do setor PINTURA (centro custo 8010) devem ser rateados somente para as sequências movimentadas no setor 3081. Critério de rateio deve ser proporcional de custo FTF dos setores 3081 + 3082 + 8010. </t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>27379</t>
-  </si>
-  <si>
-    <t>Interface Planilhas Custeio Gerencial x Sistema de Custeio - Acompanhamento</t>
-  </si>
-  <si>
-    <t>05/05/2025</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>9704480615</t>
-  </si>
-  <si>
-    <t>Registro K260 – Registro da produção refugada</t>
-  </si>
-  <si>
-    <t>30/07/2025</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>33077</t>
-  </si>
-  <si>
-    <t>Sistema de Panelas</t>
-  </si>
-  <si>
-    <t>25/07/2025</t>
-  </si>
-  <si>
-    <t>PDI - Fixar colunas de identificação das cotas</t>
-  </si>
-  <si>
-    <t>33304</t>
-  </si>
-  <si>
-    <t>Sistema de cadastro</t>
-  </si>
-  <si>
-    <t>08/08/2025</t>
-  </si>
-  <si>
-    <t>33009</t>
-  </si>
-  <si>
-    <t>Controle de indicadores ao vivo</t>
-  </si>
-  <si>
-    <t>26571</t>
-  </si>
-  <si>
-    <t>Retirar de peças do deposito para versão WMS</t>
-  </si>
-  <si>
-    <t>33333</t>
-  </si>
-  <si>
-    <t>Teste com Trigger - Checagem do fechamento do custo</t>
-  </si>
-  <si>
-    <t>33618</t>
-  </si>
-  <si>
-    <t>Bloco K - Ajuste no filtro de seleção das sequências oriundas do cálculo do custo.</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Integração CRM - Tarefa para disparar integrações</t>
-  </si>
-  <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
@@ -306,25 +321,31 @@
     <t>Integração CRM - Carga Cliente</t>
   </si>
   <si>
-    <t>33044</t>
+    <t>9889920136</t>
   </si>
   <si>
     <t>Correção dos motivos de paradas</t>
   </si>
   <si>
-    <t>33584</t>
+    <t>01/09/2025</t>
+  </si>
+  <si>
+    <t>9879722077</t>
   </si>
   <si>
     <t>Data de Fusão - Validação de Solda</t>
   </si>
   <si>
-    <t>33331</t>
+    <t>28/08/2025</t>
+  </si>
+  <si>
+    <t>9778013081</t>
   </si>
   <si>
     <t>Criação de campo no ERP CÓDIGO DISPOSITIVO</t>
   </si>
   <si>
-    <t>33551</t>
+    <t>9879756323</t>
   </si>
   <si>
     <t>Ajuste Sistema MPO - Usinagem</t>
@@ -348,43 +369,43 @@
     <t>17/03/2026</t>
   </si>
   <si>
-    <t>33420</t>
+    <t>9880310678</t>
   </si>
   <si>
     <t>Adição de Coluna no gráfico do refugo</t>
   </si>
   <si>
-    <t>31794</t>
+    <t>9889620548</t>
   </si>
   <si>
     <t>Inclusão de romaneios manualmente no Recibo de Embarque</t>
   </si>
   <si>
-    <t>33390</t>
+    <t>9880478602</t>
   </si>
   <si>
     <t>Solicitação de Verificação de Desempenho – Sistema WMS</t>
   </si>
   <si>
-    <t>29123</t>
+    <t>9889596381</t>
   </si>
   <si>
     <t>B.I ordens de manutenção maquinas pneumáticas</t>
   </si>
   <si>
-    <t>33271</t>
+    <t>9778107398</t>
   </si>
   <si>
     <t>Extração de dados IROG Usinagem</t>
   </si>
   <si>
-    <t>33410</t>
+    <t>9880416979</t>
   </si>
   <si>
     <t>Relatório de notas excluídas da portaria</t>
   </si>
   <si>
-    <t>32536</t>
+    <t>9683896530</t>
   </si>
   <si>
     <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM</t>
@@ -393,13 +414,16 @@
     <t>28/07/2025</t>
   </si>
   <si>
-    <t>33123</t>
+    <t>9778603139</t>
   </si>
   <si>
     <t>Adicionar coluna no Planilhão de RX</t>
   </si>
   <si>
-    <t>33599</t>
+    <t>31/08/2025</t>
+  </si>
+  <si>
+    <t>9879661029</t>
   </si>
   <si>
     <t>Correção</t>
@@ -411,6 +435,9 @@
     <t>29853</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
   </si>
   <si>
@@ -423,49 +450,49 @@
     <t>ADH</t>
   </si>
   <si>
-    <t>33388</t>
+    <t>9880493946</t>
   </si>
   <si>
     <t>Solicitação de Alteração no Sistema WMS – Separação de Pick List de Ordens Históricas</t>
   </si>
   <si>
-    <t>31836</t>
+    <t>9889620663</t>
   </si>
   <si>
     <t>Melhoria WMS - Conferencia e Carregamento</t>
   </si>
   <si>
-    <t>32395</t>
+    <t>9880714501</t>
   </si>
   <si>
     <t>Liberação de Embarque Com Pendencia</t>
   </si>
   <si>
-    <t>33189</t>
+    <t>9880698596</t>
   </si>
   <si>
     <t>Relatório ofertas perdidas</t>
   </si>
   <si>
-    <t>33446</t>
+    <t>9880196199</t>
   </si>
   <si>
     <t>APONTAMENTO ELETRONICO JATO</t>
   </si>
   <si>
-    <t>33668</t>
+    <t>9881214831</t>
   </si>
   <si>
     <t>Analise de OCs para o Benner - construção do fluxo de caixa</t>
   </si>
   <si>
-    <t>33550</t>
+    <t>9879768650</t>
   </si>
   <si>
     <t>Correção Sistema MPO-Usinagem</t>
   </si>
   <si>
-    <t>33401</t>
+    <t>9880448583</t>
   </si>
   <si>
     <t>Gráfico refugo diário - SENSE</t>
@@ -477,79 +504,79 @@
     <t>Chamada de aplicações pelo HUB</t>
   </si>
   <si>
-    <t>33391</t>
+    <t>9880466833</t>
   </si>
   <si>
     <t>Apontamento de solda Digital</t>
   </si>
   <si>
-    <t>32223</t>
+    <t>9880751162</t>
   </si>
   <si>
     <t>Erro no registro da macharia</t>
   </si>
   <si>
-    <t>33270</t>
+    <t>9778122182</t>
   </si>
   <si>
     <t>Extração de dados Setup de máquinas</t>
   </si>
   <si>
-    <t>33519</t>
+    <t>9879885626</t>
   </si>
   <si>
     <t>Backlog de alterações - Sistema Manutenção -&gt; SS e OS</t>
   </si>
   <si>
-    <t>33148</t>
+    <t>9778590791</t>
   </si>
   <si>
     <t>FORMULÁRIOS AP119 - IMPRESSÃO</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>9889620903</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
   </si>
   <si>
-    <t>33244</t>
+    <t>9778279415</t>
   </si>
   <si>
     <t>Integração do mapeamento digital com sistema do PCP</t>
   </si>
   <si>
-    <t>31632</t>
+    <t>9787329732</t>
   </si>
   <si>
     <t>Criação Dupla de Sequencias</t>
   </si>
   <si>
-    <t>33472</t>
+    <t>9880081235</t>
   </si>
   <si>
     <t>PAINEL MANIPULADORES</t>
   </si>
   <si>
-    <t>33691</t>
+    <t>9881175578</t>
   </si>
   <si>
     <t>Painel de prazo de lançamento de notas</t>
   </si>
   <si>
-    <t>33474</t>
+    <t>9879817463</t>
   </si>
   <si>
     <t>Relatórios Customizados</t>
   </si>
   <si>
-    <t>33451</t>
+    <t>9880113682</t>
   </si>
   <si>
     <t>IROG JATO GANCHEIRA</t>
   </si>
   <si>
-    <t>32310</t>
+    <t>9889919955</t>
   </si>
   <si>
     <t>Retrabalho da moldagem - Classificação</t>
@@ -567,55 +594,55 @@
     <t>02/06/2026</t>
   </si>
   <si>
-    <t>32584</t>
+    <t>9889919707</t>
   </si>
   <si>
     <t>Sistema para monitoramento de ruído</t>
   </si>
   <si>
-    <t>33659</t>
+    <t>9881405188</t>
   </si>
   <si>
     <t>Orçamento</t>
   </si>
   <si>
-    <t>33663</t>
+    <t>9881305003</t>
   </si>
   <si>
     <t>Colunas auxiliares</t>
   </si>
   <si>
-    <t>33511</t>
+    <t>9879947782</t>
   </si>
   <si>
     <t>Performance Multidirecional Komatsu</t>
   </si>
   <si>
-    <t>33161</t>
+    <t>9889621044</t>
   </si>
   <si>
     <t>Prioridade no sistema pré-lista por rua-prédio-nível</t>
   </si>
   <si>
-    <t>31757</t>
+    <t>9787745966</t>
   </si>
   <si>
     <t>Performance SPS</t>
   </si>
   <si>
-    <t>33658</t>
+    <t>9881434776</t>
   </si>
   <si>
     <t>MPO ajustagem</t>
   </si>
   <si>
-    <t>33662</t>
+    <t>9881334201</t>
   </si>
   <si>
     <t>Controle de documentação de exportação</t>
   </si>
   <si>
-    <t>32853</t>
+    <t>9889773907</t>
   </si>
   <si>
     <t>Ajuste Polaris - Item Cadastros</t>
@@ -627,103 +654,118 @@
     <t>Apresentação Sistema de Importação</t>
   </si>
   <si>
-    <t>33462</t>
+    <t>9880088677</t>
   </si>
   <si>
     <t>Posto de cópias eletrônico - Atualização revisão dos Doc´s</t>
   </si>
   <si>
-    <t>33687</t>
+    <t>9919043395</t>
   </si>
   <si>
     <t>Followup pacotes</t>
   </si>
   <si>
-    <t>28/08/2025</t>
-  </si>
-  <si>
-    <t>33499</t>
+    <t>9879983919</t>
   </si>
   <si>
     <t>Adição de campo tempo médio</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>9889774056</t>
   </si>
   <si>
     <t>Conversão KB TOTO</t>
   </si>
   <si>
-    <t>31685</t>
+    <t>9787746586</t>
   </si>
   <si>
     <t>Planilhão via Qlik sense</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>9904963124</t>
   </si>
   <si>
     <t>Integrar peso do recibo de embarque ao agendamento de saída e atualizar o status para concluído</t>
   </si>
   <si>
-    <t>26/08/2025</t>
+    <t>9904984376</t>
   </si>
   <si>
     <t>Criar opção para incluir anexo no agendamento</t>
   </si>
   <si>
+    <t>9904986199</t>
+  </si>
+  <si>
     <t>Flexibilidade de horário no almoxarifado e industrialização</t>
   </si>
   <si>
+    <t>9904988134</t>
+  </si>
+  <si>
     <t>Opção para buscar cliente e transportador</t>
   </si>
   <si>
+    <t>9904989511</t>
+  </si>
+  <si>
     <t>Filtro de expedidor na tela de consulta do agendamento</t>
   </si>
   <si>
+    <t>9904990549</t>
+  </si>
+  <si>
     <t>Obrigatoriedade dos campos de peso</t>
   </si>
   <si>
+    <t>9904998203</t>
+  </si>
+  <si>
     <t>Verificar o horário do agendamento, caso o mesmo seja cancelado</t>
   </si>
   <si>
-    <t>33288</t>
+    <t>9778083738</t>
   </si>
   <si>
     <t>FTF Qualidade</t>
   </si>
   <si>
-    <t>32287</t>
+    <t>9788042273</t>
   </si>
   <si>
     <t>Aplicação de controle de consumo e custo de PROEX e Antecipação de Caterpillar - Reunião</t>
   </si>
   <si>
-    <t>33264</t>
+    <t>10/08/2025</t>
+  </si>
+  <si>
+    <t>9778229091</t>
   </si>
   <si>
     <t>Aplicação IROG - Usinagem (Indicadores de Paradas)</t>
   </si>
   <si>
-    <t>33710</t>
+    <t>9921670512</t>
   </si>
   <si>
     <t>PARADAS DE APONTAMENTO ELETRONICO JATOS</t>
   </si>
   <si>
-    <t>33516</t>
+    <t>9879923322</t>
   </si>
   <si>
     <t>Melhoria no sistema de cadastro de modelos, no histórico de conserto de modelos</t>
   </si>
   <si>
-    <t>33517</t>
+    <t>9879904140</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DE MODELO EM FTF</t>
   </si>
   <si>
-    <t>33581</t>
+    <t>9879745517</t>
   </si>
   <si>
     <t>MODELO CLIENTE NA FTF</t>
@@ -735,7 +777,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-18</t>
+    <t>Mai/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1327,42 +1369,42 @@
         <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>21</v>
@@ -1374,19 +1416,19 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -1394,113 +1436,113 @@
         <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="O5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1512,89 +1554,89 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1609,39 +1651,39 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1656,39 +1698,39 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M9" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1700,89 +1742,89 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1794,42 +1836,42 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1841,89 +1883,89 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1938,39 +1980,39 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1982,89 +2024,89 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="M17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2076,42 +2118,42 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -2126,39 +2168,39 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2170,183 +2212,183 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2361,39 +2403,39 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2405,89 +2447,89 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="M26" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2499,89 +2541,89 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2593,42 +2635,42 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2643,39 +2685,39 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M30" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2687,42 +2729,42 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2737,39 +2779,39 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L32" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M32" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2781,42 +2823,42 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M33" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2828,42 +2870,42 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2875,42 +2917,42 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="K35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M35" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2922,42 +2964,42 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2969,89 +3011,89 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M37" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -3063,42 +3105,42 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3113,39 +3155,39 @@
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M40" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3157,42 +3199,42 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3204,42 +3246,42 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3251,42 +3293,42 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3298,42 +3340,42 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3345,42 +3387,42 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3392,42 +3434,42 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3442,39 +3484,39 @@
         <v>23</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3486,42 +3528,42 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3533,42 +3575,42 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3580,42 +3622,42 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3627,42 +3669,42 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K51" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L51" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M51" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3674,42 +3716,42 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3724,39 +3766,39 @@
         <v>23</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3768,42 +3810,42 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K54" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M54" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3815,42 +3857,42 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3862,42 +3904,42 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3909,42 +3951,42 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3956,42 +3998,42 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -4003,45 +4045,45 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>21</v>
@@ -4053,86 +4095,86 @@
         <v>23</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4147,39 +4189,39 @@
         <v>23</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4191,42 +4233,42 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4238,42 +4280,42 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4285,42 +4327,42 @@
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4335,39 +4377,39 @@
         <v>23</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4379,42 +4421,42 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4426,42 +4468,42 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4473,42 +4515,42 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4523,39 +4565,39 @@
         <v>23</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
@@ -4567,42 +4609,42 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
@@ -4614,45 +4656,45 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>21</v>
@@ -4661,42 +4703,42 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4708,42 +4750,42 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4758,39 +4800,39 @@
         <v>23</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
@@ -4802,27 +4844,27 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
@@ -4834,10 +4876,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
@@ -4849,27 +4891,27 @@
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -4881,10 +4923,10 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -4896,27 +4938,27 @@
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
@@ -4928,10 +4970,10 @@
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
@@ -4943,27 +4985,27 @@
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
@@ -4975,10 +5017,10 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -4990,27 +5032,27 @@
         <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
@@ -5022,10 +5064,10 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -5037,27 +5079,27 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
@@ -5069,10 +5111,10 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
@@ -5084,27 +5126,27 @@
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
@@ -5116,10 +5158,10 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5131,42 +5173,42 @@
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>217</v>
+        <v>55</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5178,42 +5220,42 @@
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K84" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L84" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L84" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M84" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5225,42 +5267,42 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K85" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="L85" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L85" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M85" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5272,42 +5314,42 @@
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
@@ -5319,42 +5361,42 @@
         <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>20</v>
@@ -5366,42 +5408,42 @@
         <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
@@ -5413,42 +5455,42 @@
         <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
@@ -5460,22 +5502,22 @@
         <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -5491,23 +5533,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5515,16 +5557,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5535,20 +5577,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>219</v>
+        <v>12.95</v>
       </c>
       <c r="J5" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K22">
         <v>54</v>
@@ -5556,7 +5598,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -5564,7 +5606,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5595,12 +5637,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="B2">
         <v>89</v>
@@ -5614,35 +5656,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>219</v>
+        <v>12.95</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5650,45 +5692,45 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N10">
         <v>54</v>
       </c>
       <c r="P10" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="Q10">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -5697,25 +5739,25 @@
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H11">
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K11">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N11">
         <v>21</v>
       </c>
       <c r="P11" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -5723,13 +5765,13 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -5741,65 +5783,71 @@
         <v>79</v>
       </c>
       <c r="J12" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="K12">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q12">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N13">
         <v>6</v>
       </c>
       <c r="P13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="G14" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -5815,7 +5863,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5823,7 +5871,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5831,10 +5879,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5842,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5850,142 +5898,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>204</v>
+        <v>394</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
